--- a/forms/trg/Formulir_TRG_indofootcare.xlsx
+++ b/forms/trg/Formulir_TRG_indofootcare.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B28)</f>
+        <f>COUNTA(Anggota!B5:B29)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F28)</f>
+        <f>COUNTA(Anggota!F5:F29)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,27 +925,31 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Asri</t>
+          <t>Dr. Takdir Tahir., S.Kep.,Ns., M.Kes</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Bachelor of Nursing</t>
-        </is>
-      </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-9356-1242</t>
+        </is>
+      </c>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57193349327</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -958,7 +962,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Andi Batari Putri Ramadhani</t>
+          <t>Asri</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -991,7 +995,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Rezky Salsabila</t>
+          <t>Andi Batari Putri Ramadhani</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1024,7 +1028,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Hidayat</t>
+          <t>Rezky Salsabila</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -1057,7 +1061,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Syamsul Alam</t>
+          <t>Muhammad Hidayat</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1068,7 +1072,7 @@
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Master of Nursing Student</t>
+          <t>Bachelor of Nursing</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1090,7 +1094,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Zulfiqar</t>
+          <t>Syamsul Alam</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1123,7 +1127,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Jibril</t>
+          <t>Muhammad Zulfiqar</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1156,7 +1160,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Ridwan</t>
+          <t>Jibril</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1189,7 +1193,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Samuel L Siagian</t>
+          <t>Ridwan</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1222,7 +1226,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Aulia Anbyah Tuanaya</t>
+          <t>Samuel L Siagian</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1233,7 +1237,7 @@
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Bachelor of Nursing</t>
+          <t>Master of Nursing Student</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1255,7 +1259,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Nur Badryyah</t>
+          <t>Aulia Anbyah Tuanaya</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1288,7 +1292,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Berliana Alfi Syahri</t>
+          <t>Nur Badryyah</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1319,10 +1323,22 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Berliana Alfi Syahri</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D17" s="12" t="n"/>
-      <c r="E17" s="11" t="n"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Bachelor of Nursing</t>
+        </is>
+      </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -1330,7 +1346,11 @@
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1519,15 +1539,32 @@
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="12" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
